--- a/output/full_scan/batch_seq7_2026-06-05.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-05.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>916.1698040585328</v>
+        <v>1086.169804058533</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>78.09999999999999</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.919875053021</v>
+        <v>58.91987501894619</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.76655018336463</v>
+        <v>14.76655022830816</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.116980405853297</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.6382124903262048</v>
+        <v>-0.6382124907078079</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>846.7212122608646</v>
+        <v>1016.721212260865</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>48.95</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.54736280920586</v>
+        <v>59.54736278146491</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14.49021154788251</v>
+        <v>14.49021151841785</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4.172121226086461</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.094795114580071</v>
+        <v>0.0947951150761403</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6525</v>
+        <v>6585</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>810.0518268676769</v>
+        <v>1000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.07140483159803</v>
+        <v>77.45267429111172</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.93738593891965</v>
+        <v>38.0646931288349</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.505182686767692</v>
+        <v>5.067459797972098</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.947007711737574</v>
+        <v>1.595974212077643</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6585</v>
+        <v>6698</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>800</v>
+        <v>995.6030601291592</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>112</v>
+        <v>45.75</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>77.45267413994779</v>
+        <v>81.02303034907047</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>38.06469306398096</v>
+        <v>42.36667982702696</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.067459797972098</v>
+        <v>2.560306012915926</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.595974212363834</v>
+        <v>1.260652970460663</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6698</v>
+        <v>6763</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>795.6030601291593</v>
+        <v>985</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45.75</v>
+        <v>50.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>81.02303031222513</v>
+        <v>69.57294048177575</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>42.36667985430668</v>
+        <v>21.41695603913639</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.560306012915926</v>
+        <v>8.137997002018212</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.260652970489284</v>
+        <v>0.5913740820987841</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6763</v>
+        <v>6761</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>785</v>
+        <v>935.4510774047476</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50.4</v>
+        <v>219</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.57294043431735</v>
+        <v>58.33604122571961</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21.41695576058588</v>
+        <v>31.921767336309</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.137997002018212</v>
+        <v>1.045107740474763</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.5913740818316724</v>
+        <v>0.4287058065517186</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6666</v>
+        <v>6693</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>763.6444375338972</v>
+        <v>932.7722762562812</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>42.35</v>
+        <v>158</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>62.02660476239029</v>
+        <v>60.62902069475334</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.08846814478641</v>
+        <v>35.35749594544829</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.364443753389716</v>
+        <v>1.777227625628113</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1928070180363437</v>
+        <v>0.3332004525365044</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6792</v>
+        <v>6517</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>759.2210503980374</v>
+        <v>915</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>72.8</v>
+        <v>69.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.66488384302372</v>
+        <v>73.23411454831654</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>44.26996279611181</v>
+        <v>19.60190291655268</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9221050398037368</v>
+        <v>5.917181772948917</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3551774508942271</v>
+        <v>0.6778887324758148</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6761</v>
+        <v>6666</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>745.4510774047476</v>
+        <v>903.6444375338972</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>219</v>
+        <v>42.35</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.33604120892198</v>
+        <v>62.02660486211721</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.92176734850117</v>
+        <v>14.08846817724088</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.045107740474763</v>
+        <v>2.364443753389716</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4287058062273754</v>
+        <v>0.1928070181031215</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6716</v>
+        <v>6669</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>697.100546592502</v>
+        <v>899.1450440878392</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>101</v>
+        <v>5660</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>53.64530945097131</v>
+        <v>61.86414615874567</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45.852545879639</v>
+        <v>29.48855201637125</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7100546592502002</v>
+        <v>0.9145044087839206</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.014694518297263</v>
+        <v>-5.658162517089863</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6693</v>
+        <v>6811</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>687.7722762562811</v>
+        <v>897.5915656274627</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>158</v>
+        <v>238.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.62902067518763</v>
+        <v>67.78937807866924</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35.35749595181138</v>
+        <v>34.41560472820898</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.777227625628113</v>
+        <v>1.25915656274627</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.3332004524792546</v>
+        <v>2.952324624692436</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6642</v>
+        <v>6792</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>682.7027504754939</v>
+        <v>874.2210503980374</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>85.3</v>
+        <v>72.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.28687246442761</v>
+        <v>68.66488384823319</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>53.9375524247272</v>
+        <v>44.26996284262735</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7702750475493823</v>
+        <v>0.9221050398037368</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.8229064019760992</v>
+        <v>0.3551774510182559</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6831</v>
+        <v>6577</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>680.4535484065991</v>
+        <v>872.75564714493</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>739</v>
+        <v>82.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.04747694882858</v>
+        <v>62.99523218406029</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.98033944428306</v>
+        <v>17.20821764477726</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.045354840659915</v>
+        <v>2.275564714493001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-15.82782526810482</v>
+        <v>0.1870134772451551</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6491</v>
+        <v>6770</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>677.249834360354</v>
+        <v>844.0145668110896</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>324.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>69.59662852688867</v>
+        <v>55.74312113551663</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>42.51306024365726</v>
+        <v>34.33748649183593</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7249834360353997</v>
+        <v>0.4014566811089576</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.24215494137629</v>
+        <v>0.8708598667618297</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6538</v>
+        <v>6525</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>676.8316275578146</v>
+        <v>810.0518268676769</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.39605052434505</v>
+        <v>60.07140484299254</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>52.76228570974842</v>
+        <v>34.93738589019071</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6831627557814669</v>
+        <v>1.505182686767692</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4351026388346302</v>
+        <v>-0.9470077115658696</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6579</v>
+        <v>6491</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>675.0394343396256</v>
+        <v>792.249834360354</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>162.5</v>
+        <v>324.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.47856854393815</v>
+        <v>69.59662852688867</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46.67176338156678</v>
+        <v>42.51306032672759</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5039434339625583</v>
+        <v>0.7249834360353997</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.9152523748430036</v>
+        <v>1.242154942521079</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6742</v>
+        <v>6592</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>674.53794196016</v>
+        <v>791.8580799945339</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.01916907599277</v>
+        <v>69.70306423915046</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>43.9770768262055</v>
+        <v>24.95950658064158</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4537941960159936</v>
+        <v>1.18580799945339</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1975886121353731</v>
+        <v>0.5939639981178851</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6651</v>
+        <v>6782</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>673.9652558824903</v>
+        <v>787.5829108293227</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>141</v>
+        <v>200.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>59.6624998832963</v>
+        <v>53.15797026452683</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46.27688606254129</v>
+        <v>13.52820158102832</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3965255882490229</v>
+        <v>0.7582910829322672</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.9803147019261312</v>
+        <v>1.499177184785892</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6834</v>
+        <v>6505</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>672.1143757750302</v>
+        <v>782.2686302202944</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>70</v>
+        <v>55.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.45928384336149</v>
+        <v>57.88752358012482</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>51.61749731049668</v>
+        <v>18.57811655695387</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2114375775030193</v>
+        <v>1.226863022029444</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.5106888442171957</v>
+        <v>0.7462528935203935</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6605</v>
+        <v>6831</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>670.065710005108</v>
+        <v>775.4535484065991</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>146</v>
+        <v>739</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>68.53135542746003</v>
+        <v>59.04747694859883</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.39394589113007</v>
+        <v>37.98033942781832</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.506571000510801</v>
+        <v>1.045354840659915</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.61342763763262</v>
+        <v>-15.82782526814296</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6577</v>
+        <v>6645</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>667.75564714493</v>
+        <v>762.2215750431295</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>82.2</v>
+        <v>12.95</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>62.99523203890993</v>
+        <v>61.77878547019598</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17.20821760729229</v>
+        <v>30.15129370941383</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.275564714493001</v>
+        <v>3.222157504312952</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1870134766727594</v>
+        <v>0.115453581373245</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6669</v>
+        <v>6605</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>664.1450440878392</v>
+        <v>760.065710005108</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>5660</v>
+        <v>146</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.86414617962733</v>
+        <v>68.53135547631386</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.48855198123352</v>
+        <v>26.39394612451647</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9145044087839206</v>
+        <v>1.506571000510801</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-5.658162518998012</v>
+        <v>1.613427638491208</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6613</v>
+        <v>6670</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>662.5571574399314</v>
+        <v>759.7870499844843</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.72557407528307</v>
+        <v>60.19146940221088</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.6914286771791</v>
+        <v>25.61782988582425</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7557157439931458</v>
+        <v>0.9787049984484318</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.193104453220105</v>
+        <v>2.234598567952331</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6672</v>
+        <v>6558</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>661.2868457249527</v>
+        <v>758.6248619892025</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>219</v>
+        <v>33.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.85147686811418</v>
+        <v>57.24396019230839</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>34.38943363656103</v>
+        <v>41.12358145205584</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.628684572495274</v>
+        <v>0.8624861989202439</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.516976025670445</v>
+        <v>0.1186682602359127</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6770</v>
+        <v>6548</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>658.810873195203</v>
+        <v>756.5674446939726</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.74312113983108</v>
+        <v>76.21334371559439</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.33748667363513</v>
+        <v>42.43035584973619</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3810873195203031</v>
+        <v>0.6567444693972613</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.8708598666568834</v>
+        <v>4.161414996077228</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6821</v>
+        <v>6556</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>657.350801388214</v>
+        <v>754.1501698817848</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>68</v>
+        <v>72.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>63.19070455156471</v>
+        <v>61.40142496392143</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.07856719320519</v>
+        <v>40.18994401415872</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.235080138821399</v>
+        <v>0.4150169881784741</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.7133325426239998</v>
+        <v>0.206085290363988</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6517</v>
+        <v>6821</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>625</v>
+        <v>747.350801388214</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.3</v>
+        <v>68</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>73.23411443710071</v>
+        <v>63.1907045986464</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.60190291213857</v>
+        <v>30.07856712402147</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5.917181772948917</v>
+        <v>0.235080138821399</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.677888732628452</v>
+        <v>0.7133325427766355</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6558</v>
+        <v>6743</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>618.6248619892025</v>
+        <v>743.0237158508507</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>33.2</v>
+        <v>30.25</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.24396001175035</v>
+        <v>64.27402442795551</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>41.12358142593563</v>
+        <v>30.9739773099192</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8624861989202439</v>
+        <v>0.8023715850850807</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1186682600164973</v>
+        <v>-0.0249565993851519</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6556</v>
+        <v>6768</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>614.1501698817848</v>
+        <v>729.0975713441336</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>72.5</v>
+        <v>95.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>61.40142505610874</v>
+        <v>67.30144239879667</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>40.1899440434452</v>
+        <v>23.69856567117074</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4150169881784741</v>
+        <v>0.909757134413364</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2060852898679089</v>
+        <v>1.442939361444024</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6695</v>
+        <v>6606</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>612.8599319228063</v>
+        <v>723.2837207537638</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>52.8</v>
+        <v>26.45</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.72505623320485</v>
+        <v>68.99331251035341</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35.24816856993453</v>
+        <v>28.482002093847</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2859931922806302</v>
+        <v>1.328372075376375</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.8338408873611032</v>
+        <v>0.1442875042390171</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6606</v>
+        <v>6776</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>608.2837207537638</v>
+        <v>720.2933388167252</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>26.45</v>
+        <v>61.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>68.99331234419826</v>
+        <v>60.74329228215381</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>28.48200252062453</v>
+        <v>13.5599441552508</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.328372075376375</v>
+        <v>1.529333881672514</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1442875042580981</v>
+        <v>0.391459401693049</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6811</v>
+        <v>6526</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>607.5915656274627</v>
+        <v>718.5170884133262</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>238.5</v>
+        <v>669</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>67.78937806126947</v>
+        <v>50.87059538370674</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>34.41560465849911</v>
+        <v>24.05174550181954</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.25915656274627</v>
+        <v>0.3517088413326208</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.952324623166081</v>
+        <v>-7.988921663454711</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6743</v>
+        <v>6560</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>603.0237158508507</v>
+        <v>710.3105157613628</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>30.25</v>
+        <v>40.05</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>64.27402427893867</v>
+        <v>58.53810431250959</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>30.97397727947284</v>
+        <v>18.78730325965774</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8023715850850807</v>
+        <v>1.531051576136284</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.024956599547326</v>
+        <v>0.2420481290342269</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6531</v>
+        <v>6690</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>601.1009108752638</v>
+        <v>702.3278094493504</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1010</v>
+        <v>182</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.00980532047875</v>
+        <v>65.94917658592666</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.72158607778052</v>
+        <v>23.60647172278713</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6100910875263856</v>
+        <v>1.232780944935046</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-17.33989322159802</v>
+        <v>1.482592359655262</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6719</v>
+        <v>6716</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>600.6885707028168</v>
+        <v>697.100546592502</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>238.5</v>
+        <v>101</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.92121892443953</v>
+        <v>53.64530947808502</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>57.99946091381371</v>
+        <v>45.85254586158718</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5688570702816842</v>
+        <v>0.7100546592502002</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-2.053949031175528</v>
+        <v>-1.01469451833542</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6546</v>
+        <v>6654</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>600.5524585540236</v>
+        <v>696.9693092565705</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>171</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.01041888473399</v>
+        <v>88.1800478657359</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.84936786746494</v>
+        <v>44.32537302762633</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5552458554023607</v>
+        <v>0.6969309256570437</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.012007689352341</v>
+        <v>6.297675048741628</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6706</v>
+        <v>6546</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>599.8895397641984</v>
+        <v>690.5524585540236</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>190</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.19625623197101</v>
+        <v>53.01041891231485</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26.92829036787569</v>
+        <v>27.84936813081523</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4889539764198361</v>
+        <v>0.5552458554023607</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.7490141022787657</v>
+        <v>0.0120076904780321</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6488</v>
+        <v>6642</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>599.0776610215379</v>
+        <v>682.7027504754939</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>811</v>
+        <v>85.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.23335027640638</v>
+        <v>62.28687250059052</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>28.5561012663025</v>
+        <v>53.93755240176578</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4077661021537848</v>
+        <v>0.7702750475493823</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-4.655882921675683</v>
+        <v>-0.8229064020524177</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6573</v>
+        <v>6538</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>589.0577075487546</v>
+        <v>676.8316275578146</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>16.1</v>
+        <v>123</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.48975417008329</v>
+        <v>61.39605051491642</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.10127845871408</v>
+        <v>52.76228585807908</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.905770754875461</v>
+        <v>0.6831627557814669</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.3157027469335131</v>
+        <v>0.4351026395787301</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6782</v>
+        <v>6579</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>572.5829108293227</v>
+        <v>675.0394343396256</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>200.5</v>
+        <v>162.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.15797029567486</v>
+        <v>61.4785685773841</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.52820156078842</v>
+        <v>46.67176343458447</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7582910829322672</v>
+        <v>0.5039434339625583</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.499177183450342</v>
+        <v>-0.9152523742705831</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6560</v>
+        <v>6742</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>570.3105157613628</v>
+        <v>674.53794196016</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>40.05</v>
+        <v>58</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.538104368315</v>
+        <v>60.01916912894253</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.78730341804012</v>
+        <v>43.97707685416231</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.531051576136284</v>
+        <v>0.4537941960159936</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2420481285286174</v>
+        <v>0.1975886123166299</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6668</v>
+        <v>6651</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>562.8690808647709</v>
+        <v>673.9652558824903</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>39</v>
+        <v>141</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.46276076157778</v>
+        <v>59.6624998832963</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.30152689542564</v>
+        <v>46.27688613031246</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7869080864770945</v>
+        <v>0.3965255882490229</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.1735053303578578</v>
+        <v>-0.9803147012201912</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6548</v>
+        <v>6834</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>556.5674446939726</v>
+        <v>672.1143757750302</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>89.7</v>
+        <v>70</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>76.21334368580064</v>
+        <v>59.45928385190129</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>42.43035590837381</v>
+        <v>51.61749725466549</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6567444693972613</v>
+        <v>0.2114375775030193</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>4.16141499617262</v>
+        <v>-0.5106888442076603</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6756</v>
+        <v>6613</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>548.8432810913666</v>
+        <v>662.5571574399314</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>95.3</v>
+        <v>262</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.37577453271109</v>
+        <v>56.72557408794008</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>42.0660899021788</v>
+        <v>28.69142862917671</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.384328109136665</v>
+        <v>0.7557157439931458</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.549201475712391</v>
+        <v>-1.193104452743144</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6670</v>
+        <v>6672</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>544.7870499844844</v>
+        <v>661.2868457249527</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>60.19146912804207</v>
+        <v>61.8514768811004</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.61782988193038</v>
+        <v>34.38943355375351</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.9787049984484318</v>
+        <v>0.628684572495274</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>2.23459857014649</v>
+        <v>0.5169760259757084</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6799</v>
+        <v>6668</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>540.6760309994409</v>
+        <v>652.8690808647709</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.89123208504642</v>
+        <v>53.46276095536415</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>39.59005871423291</v>
+        <v>30.30152691244999</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5676030999440812</v>
+        <v>0.7869080864770945</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.110915401022308</v>
+        <v>-0.1735053305486532</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6494</v>
+        <v>6805</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>539.4632518147525</v>
+        <v>631.7576281106543</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>56.5</v>
+        <v>1950</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,29 +2990,29 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.68680378407666</v>
+        <v>52.28495369451837</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>32.13675861616446</v>
+        <v>16.65165109427005</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4463251814752551</v>
+        <v>0.6757628110654321</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.1966396194889383</v>
+        <v>24.98983037609229</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>538.4245532856739</v>
+        <v>628.4245532856739</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>472.5</v>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.08509667688369</v>
+        <v>44.08509667881707</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>29.76238296013377</v>
+        <v>29.76238295807516</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.8424553285673945</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-18.99723400694581</v>
+        <v>-18.99723400690766</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6598</v>
+        <v>6840</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>533.102307113501</v>
+        <v>616.2170578525471</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>24.5</v>
+        <v>69.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.74078228227704</v>
+        <v>58.62808478830709</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>34.6887479558184</v>
+        <v>21.78682753963077</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8102307113501003</v>
+        <v>0.6217057852547138</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0455578910344625</v>
+        <v>0.9443120028953504</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6690</v>
+        <v>6581</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>532.3278094493505</v>
+        <v>615.4275239331314</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>65.94917655327644</v>
+        <v>55.87571991452445</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.6064720451884</v>
+        <v>16.32347510878058</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.232780944935046</v>
+        <v>0.5427523933131441</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.48259235870129</v>
+        <v>0.3675360125306945</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6592</v>
+        <v>6695</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>531.8580799945339</v>
+        <v>612.8599319228063</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>65</v>
+        <v>52.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>69.70306410908691</v>
+        <v>49.7250562738074</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24.9595064750308</v>
+        <v>35.24816849172009</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.18580799945339</v>
+        <v>0.2859931922806302</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.5939639981751227</v>
+        <v>-0.8338408871893828</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6768</v>
+        <v>6788</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>529.0975713441337</v>
+        <v>606.3385252750043</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>95.5</v>
+        <v>430.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>67.30144224105824</v>
+        <v>53.04549429050515</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.69856565838282</v>
+        <v>11.55773648540487</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.909757134413364</v>
+        <v>1.633852527500427</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.44293936169205</v>
+        <v>-0.8424258797353668</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6552</v>
+        <v>6741</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>524.2464794722605</v>
+        <v>601.8117681480783</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>32.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.47100575970915</v>
+        <v>53.38072009969947</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.18855457872824</v>
+        <v>14.23451940853914</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4246479472260437</v>
+        <v>0.6811768148078245</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0491116924914623</v>
+        <v>0.1268299665522313</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6715</v>
+        <v>6531</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>522.9876838529335</v>
+        <v>601.1009108752638</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>434</v>
+        <v>1010</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>47.67388771924336</v>
+        <v>52.00980533527493</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>30.239912247946</v>
+        <v>34.72158601642921</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2987683852933598</v>
+        <v>0.6100910875263856</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-6.865630560266741</v>
+        <v>-17.33989322131193</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6789</v>
+        <v>6719</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>520.2775788510473</v>
+        <v>600.6885707028168</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>513</v>
+        <v>238.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.23746326157124</v>
+        <v>58.92121892443953</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.70503272261348</v>
+        <v>57.99946091424329</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5277578851047309</v>
+        <v>0.5688570702816842</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-8.965921816555994</v>
+        <v>-2.05394902983997</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6526</v>
+        <v>6706</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>508.5170884133262</v>
+        <v>599.8895397641984</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>669</v>
+        <v>190</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.87059535738184</v>
+        <v>54.19625622930512</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>24.0517454580873</v>
+        <v>26.92829028488793</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3517088413326208</v>
+        <v>0.4889539764198361</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-7.988921664790283</v>
+        <v>-0.7490141014201619</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6691</v>
+        <v>6488</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>504.6219954569681</v>
+        <v>599.0776610215379</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>642</v>
+        <v>811</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.77741306827678</v>
+        <v>52.2333502790822</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.61001049274377</v>
+        <v>28.55610119318068</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9621995456968124</v>
+        <v>0.4077661021537848</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.2710643125161702</v>
+        <v>-4.655882921389463</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6645</v>
+        <v>6689</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>502.2215750431295</v>
+        <v>590.6928117868974</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>12.95</v>
+        <v>73.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>61.77878493861562</v>
+        <v>61.1352436164271</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>30.15129363888323</v>
+        <v>20.22831509652793</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3.222157504312952</v>
+        <v>1.069281178689744</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1154535814877217</v>
+        <v>1.125755867396977</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6581</v>
+        <v>6582</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>500.4275239331315</v>
+        <v>590.2558284152253</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>110</v>
+        <v>32.15</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>55.87571973852695</v>
+        <v>63.33892247835723</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.32347511029806</v>
+        <v>21.25244630484233</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5427523933131441</v>
+        <v>1.025582841522533</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.367536012893203</v>
+        <v>0.240983606455416</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6654</v>
+        <v>6573</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>496.9693092565705</v>
+        <v>589.0577075487546</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>171</v>
+        <v>16.1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>88.18004786024196</v>
+        <v>59.48975424513358</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>44.32537301912226</v>
+        <v>20.10127842690014</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6969309256570437</v>
+        <v>0.905770754875461</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>6.297675048837036</v>
+        <v>0.3157027469144324</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6788</v>
+        <v>6679</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>491.3385252750043</v>
+        <v>571.5763065539641</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>430.5</v>
+        <v>281</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.045494282578</v>
+        <v>38.10782747792587</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11.55773651069946</v>
+        <v>29.28274040584479</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.633852527500427</v>
+        <v>0.6576306553964055</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.8424258804985101</v>
+        <v>-7.267013155029247</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6776</v>
+        <v>6794</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>490.2933388167252</v>
+        <v>561.4821775748494</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>61.2</v>
+        <v>82.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>60.7432922404967</v>
+        <v>56.66229237213074</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.55994406498044</v>
+        <v>16.40465187751417</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.529333881672514</v>
+        <v>0.6482177574849367</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3914594015785703</v>
+        <v>0.4402718238746326</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6498</v>
+        <v>6570</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>479.462447635239</v>
+        <v>557.7448633997278</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.5</v>
+        <v>58.4</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.45658513753745</v>
+        <v>64.63494636743059</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>38.59070300774651</v>
+        <v>37.40457733284655</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4462447635239004</v>
+        <v>0.2744863399727764</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.8191256476625242</v>
+        <v>0.1182656190375492</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6658</v>
+        <v>6641</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>477.3571865779249</v>
+        <v>553.6439437178947</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>188</v>
+        <v>18.75</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.39132625126329</v>
+        <v>53.48648912108135</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>56.7889150270037</v>
+        <v>25.36456082963101</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.235718657792492</v>
+        <v>1.364394371789463</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-5.361042419287998</v>
+        <v>0.0666160094176298</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6679</v>
+        <v>6756</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>476.5763065539641</v>
+        <v>548.8432810913666</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>281</v>
+        <v>95.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>38.1078274410178</v>
+        <v>48.37577456577799</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>29.28274044237422</v>
+        <v>42.06609000947418</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6576306553964055</v>
+        <v>0.384328109136665</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-7.267013156841843</v>
+        <v>-1.549201475388043</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6803</v>
+        <v>6799</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>470.5585905949642</v>
+        <v>540.6760309994409</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>289</v>
+        <v>97</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>55.2059166787329</v>
+        <v>48.89123217513258</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.33502603283419</v>
+        <v>39.5900588288014</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.055859059496422</v>
+        <v>0.5676030999440812</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.3014728342584909</v>
+        <v>-1.11091540083151</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6570</v>
+        <v>6494</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>467.7448633997278</v>
+        <v>539.4632518147525</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>58.4</v>
+        <v>56.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>64.63494634394712</v>
+        <v>52.68680380627254</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>37.404577246408</v>
+        <v>32.13675860384321</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2744863399727764</v>
+        <v>0.4463251814752551</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1182656187990556</v>
+        <v>-0.1966396192409079</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6741</v>
+        <v>6598</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>461.8117681480783</v>
+        <v>533.102307113501</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>24.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.38072040809816</v>
+        <v>57.74078243530271</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.23451910487655</v>
+        <v>34.68874793076458</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6811768148078245</v>
+        <v>0.8102307113501003</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.126829965140351</v>
+        <v>-0.0455578910630787</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6582</v>
+        <v>6541</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>450.2558284152253</v>
+        <v>532.4580040859244</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>32.15</v>
+        <v>41.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>63.33892200736893</v>
+        <v>60.75176939212189</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.2524462395098</v>
+        <v>17.74232090830129</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.025582841522533</v>
+        <v>0.7458004085924348</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2409836066557485</v>
+        <v>0.4967737976078968</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6840</v>
+        <v>6771</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>446.2170578525472</v>
+        <v>531.4814041188691</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>69.5</v>
+        <v>42.55</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>58.62808596324668</v>
+        <v>49.42160867942889</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.78682804642238</v>
+        <v>22.66645184949288</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6217057852547138</v>
+        <v>1.648140411886912</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.944311994786586</v>
+        <v>0.1004400053708656</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6532</v>
+        <v>6754</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>438.9066746651818</v>
+        <v>524.3139152122961</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>96.7</v>
+        <v>45.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.90988009495594</v>
+        <v>54.15878560188625</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>24.8290968566382</v>
+        <v>23.38331670441918</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3906674665181807</v>
+        <v>0.4313915212296145</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.189915346817705</v>
+        <v>0.2681236010482967</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6643</v>
+        <v>6552</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>435.3749695268402</v>
+        <v>524.2464794722605</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>556</v>
+        <v>32.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.08940919273569</v>
+        <v>52.47100583587275</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.76969436702018</v>
+        <v>24.18855459217376</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5374969526840182</v>
+        <v>0.4246479472260437</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-8.453650916645211</v>
+        <v>0.0491116925200774</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6664</v>
+        <v>6715</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>433.8633175414064</v>
+        <v>522.9876838529335</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>408.5</v>
+        <v>434</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.90925640390211</v>
+        <v>47.67388773286505</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.426800493559</v>
+        <v>30.23991220665596</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3863317541406394</v>
+        <v>0.2987683852933598</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-6.012602083999928</v>
+        <v>-6.865630560075969</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6505</v>
+        <v>6789</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>427.2686302202944</v>
+        <v>520.2775788510473</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>55.3</v>
+        <v>513</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>57.88752352539326</v>
+        <v>46.23746327114501</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.57811656036867</v>
+        <v>20.70503265535686</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.226863022029444</v>
+        <v>0.5277578851047309</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.7462528933868379</v>
+        <v>-8.965921815602035</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6667</v>
+        <v>6512</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>421.9519475022926</v>
+        <v>518.4253117190669</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>268.5</v>
+        <v>19.85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.55279849264284</v>
+        <v>53.19720660600188</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.00108132725138</v>
+        <v>6.247995803612055</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.695194750229257</v>
+        <v>0.3425311719066871</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>1.26136360870596</v>
+        <v>0.1957925890342319</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6805</v>
+        <v>6691</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>421.7576281106543</v>
+        <v>504.6219954569681</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1950</v>
+        <v>642</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.28495369126612</v>
+        <v>50.7774131724514</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.65165117630586</v>
+        <v>11.61001055199389</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6757628110654321</v>
+        <v>0.9621995456968124</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>24.98983037437523</v>
+        <v>-0.271064313660843</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6794</v>
+        <v>6591</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>421.4821775748493</v>
+        <v>501.595191341755</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>82.8</v>
+        <v>57.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>56.66229229074206</v>
+        <v>55.18752010193393</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.40465171365304</v>
+        <v>24.83373572051188</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6482177574849367</v>
+        <v>0.6595191341754961</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.4402718240272698</v>
+        <v>0.7447726335702562</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6732</v>
+        <v>6486</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>407.1280468091347</v>
+        <v>496.0964566722912</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>163.5</v>
+        <v>83.2</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.97944667810861</v>
+        <v>51.64787358955338</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>26.09663502143238</v>
+        <v>16.32962260714492</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7128046809134748</v>
+        <v>1.109645667229123</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-1.551053072889641</v>
+        <v>0.3370633766791153</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6689</v>
+        <v>6708</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>390.6928117868974</v>
+        <v>494.5064005552385</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>73.5</v>
+        <v>41.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>61.13524351720375</v>
+        <v>53.83365905757911</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.22831508807977</v>
+        <v>17.2681530751414</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.069281178689744</v>
+        <v>1.450640055523847</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.125755867129866</v>
+        <v>-0.0032281447314173</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6591</v>
+        <v>6790</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>386.595191341755</v>
+        <v>483.4191398018461</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>57.8</v>
+        <v>39.75</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>55.18752002904494</v>
+        <v>52.15935025168254</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.83373562145666</v>
+        <v>15.8326714864951</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6595191341754961</v>
+        <v>1.341913980184609</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.7447726335893338</v>
+        <v>0.0681004835778647</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6835</v>
+        <v>6589</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>386.4879245593252</v>
+        <v>480.0565062135913</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>38.55</v>
+        <v>44.35</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.09037648934439</v>
+        <v>47.9851553805926</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9.993608815326326</v>
+        <v>29.43063166318456</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.148792455932516</v>
+        <v>0.5056506213591336</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0285267052508288</v>
+        <v>0.6153979096287392</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6754</v>
+        <v>6498</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>384.3139152122961</v>
+        <v>479.462447635239</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>45.6</v>
+        <v>101.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>54.15878531503219</v>
+        <v>50.45658514696512</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.3833163726173</v>
+        <v>38.59070300774651</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4313915212296145</v>
+        <v>0.4462447635239004</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.268123601200932</v>
+        <v>-0.8191256475480455</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6486</v>
+        <v>6658</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>381.0964566722912</v>
+        <v>477.3571865779249</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>83.2</v>
+        <v>188</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>51.6478734891578</v>
+        <v>52.39132626901878</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.32962260074183</v>
+        <v>56.78891508962724</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.109645667229123</v>
+        <v>1.235718657792492</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.3370633766791153</v>
+        <v>-5.361042419211682</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6708</v>
+        <v>6803</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>379.5064005552385</v>
+        <v>470.5585905949642</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>41.5</v>
+        <v>289</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>53.83365894075398</v>
+        <v>55.2059167320332</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.26815311046413</v>
+        <v>15.33502606145699</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.450640055523847</v>
+        <v>1.055859059496422</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0032281447123376</v>
+        <v>0.3014728343538718</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6512</v>
+        <v>6533</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>378.4253117190669</v>
+        <v>440.7578670386552</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>19.85</v>
+        <v>221.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.19720658730975</v>
+        <v>46.69255903814044</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6.247995766389901</v>
+        <v>25.06097005449644</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3425311719066871</v>
+        <v>0.5757867038655133</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1957925890914724</v>
+        <v>-1.361688652136675</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6735</v>
+        <v>6532</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>375.8006215251692</v>
+        <v>438.9066746651818</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>100.5</v>
+        <v>96.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.66553384879495</v>
+        <v>47.90988011604392</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>27.81993070211077</v>
+        <v>24.82909692605242</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5800621525169229</v>
+        <v>0.3906674665181807</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-2.657376295291597</v>
+        <v>-1.189915346607832</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6515</v>
+        <v>6643</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>375.4494235112053</v>
+        <v>435.3749695268402</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>8425</v>
+        <v>556</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.82570847089634</v>
+        <v>44.08940922310882</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25.81146006851796</v>
+        <v>15.76969440297768</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5449423511205339</v>
+        <v>0.5374969526840182</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-146.4901558698872</v>
+        <v>-8.453650911493799</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6568</v>
+        <v>6664</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>372.1249917756055</v>
+        <v>433.8633175414064</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>203</v>
+        <v>408.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.96281739887068</v>
+        <v>44.90925647970177</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.06610406710642</v>
+        <v>19.42680033433226</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7124991775605464</v>
+        <v>0.3863317541406394</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.913470609649356</v>
+        <v>-6.012602083904546</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6790</v>
+        <v>6667</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>368.4191398018461</v>
+        <v>421.9519475022926</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>39.75</v>
+        <v>268.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.15935019886893</v>
+        <v>52.55279850624473</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.83267146190597</v>
+        <v>17.00108130445367</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.341913980184609</v>
+        <v>0.695194750229257</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0681004835683288</v>
+        <v>1.261363609659931</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6561</v>
+        <v>6625</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>364.2759488860981</v>
+        <v>418.4931429611548</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>358.5</v>
+        <v>74.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.49257690870349</v>
+        <v>56.56117330174065</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.78394500387439</v>
+        <v>17.20652580582848</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9275948886098044</v>
+        <v>0.8493142961154784</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.867568008981458</v>
+        <v>0.3909352127437835</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6541</v>
+        <v>6732</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>362.4580040859244</v>
+        <v>407.1280468091347</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>41.9</v>
+        <v>163.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>60.75176936995562</v>
+        <v>44.97944670518677</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.7423207892689</v>
+        <v>26.09663526295879</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7458004085924348</v>
+        <v>0.7128046809134748</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.4967737968637968</v>
+        <v>-1.551053071649479</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6739</v>
+        <v>6530</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>362.1181133552876</v>
+        <v>390.093785983843</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>1220</v>
+        <v>109.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.74103645450162</v>
+        <v>49.81907606104512</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.188326939532</v>
+        <v>14.55406833003458</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7118113355287545</v>
+        <v>0.5093785983842964</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-2.169192099908049</v>
+        <v>-0.2700638221575935</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6829</v>
+        <v>6807</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>359.3375464765434</v>
+        <v>387.8705653180606</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>202</v>
+        <v>33.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.48726493410485</v>
+        <v>40.36797694616587</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.81347399299312</v>
+        <v>31.65170566629388</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4337546476543346</v>
+        <v>1.287056531806067</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-2.221736879970843</v>
+        <v>0.3194534878968371</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6641</v>
+        <v>6835</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>348.6439437178946</v>
+        <v>386.4879245593252</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>18.75</v>
+        <v>38.55</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>53.48648877882749</v>
+        <v>51.09037645390585</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>25.36456080838873</v>
+        <v>9.993608882921134</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.364394371789463</v>
+        <v>1.148792455932516</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0666160093985502</v>
+        <v>-0.0285267048692421</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6584</v>
+        <v>6624</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>344.807163982987</v>
+        <v>383.5868933889687</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>650</v>
+        <v>47.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.77993455424739</v>
+        <v>52.52196924588924</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.90030110096546</v>
+        <v>15.77139494134005</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4807163982987074</v>
+        <v>0.8586893388968667</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-5.721591009284413</v>
+        <v>0.777915694380221</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6806</v>
+        <v>6735</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>340.507993028472</v>
+        <v>375.8006215251692</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>5.64</v>
+        <v>100.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>34.31641400766956</v>
+        <v>43.66553389148072</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>30.52195369749095</v>
+        <v>27.81993088107299</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5507993028471946</v>
+        <v>0.5800621525169229</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.2897227127258945</v>
+        <v>-2.657376295615947</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6589</v>
+        <v>6515</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>340.0565062135913</v>
+        <v>375.4494235112053</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>44.35</v>
+        <v>8425</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.9851553805926</v>
+        <v>43.82570847813525</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>29.43063159507962</v>
+        <v>25.81146000797003</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5056506213591336</v>
+        <v>0.5449423511205339</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.615397909342547</v>
+        <v>-146.4901558647353</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6771</v>
+        <v>6757</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>326.4814041188691</v>
+        <v>374.8741075870409</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>42.55</v>
+        <v>54.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.42160873722629</v>
+        <v>51.5898744365293</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.66645165502452</v>
+        <v>30.092159355341</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.648140411886912</v>
+        <v>2.487410758704088</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1004400051800757</v>
+        <v>-0.0359541952864101</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6533</v>
+        <v>6720</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>325.7578670386551</v>
+        <v>372.8012407180428</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>221.5</v>
+        <v>148.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.69255900986555</v>
+        <v>35.7595542131825</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>25.06096997915792</v>
+        <v>25.25649667951044</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5757867038655133</v>
+        <v>0.7801240718042758</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.36168865394926</v>
+        <v>-0.2201949974086736</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6680</v>
+        <v>6568</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>306.8850106471623</v>
+        <v>372.1249917756055</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>54.5</v>
+        <v>203</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.103477110394</v>
+        <v>40.9628174278236</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6.152176557313388</v>
+        <v>21.06610401873327</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.18850106471623</v>
+        <v>0.7124991775605464</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.9960605666066832</v>
+        <v>-1.913470609553976</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6534</v>
+        <v>6838</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>306.0075853673343</v>
+        <v>370.6330175531716</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>90.7</v>
+        <v>25.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>38.2915125683158</v>
+        <v>37.6754100553946</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.37633722399011</v>
+        <v>13.99327808860507</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6007585367334354</v>
+        <v>1.563301755317157</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.6956839760941251</v>
+        <v>0.0788478317228305</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6625</v>
+        <v>6561</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>303.4931429611548</v>
+        <v>364.2759488860981</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>74.7</v>
+        <v>358.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>56.56117347313876</v>
+        <v>51.49257705501731</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.20652540412249</v>
+        <v>17.78394498371494</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.8493142961154784</v>
+        <v>0.9275948886098044</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.3909352117898087</v>
+        <v>1.867568007932003</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6640</v>
+        <v>6796</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>298.0928945901964</v>
+        <v>364.1251216444405</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>1190</v>
+        <v>61</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>36.63103290429182</v>
+        <v>39.70397094144583</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.57529253384316</v>
+        <v>29.76924975832157</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8092894590196322</v>
+        <v>0.9125121644440513</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-21.91420700531271</v>
+        <v>0.3279777504108487</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6588</v>
+        <v>6739</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>294.1795461459866</v>
+        <v>362.1181133552876</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>109</v>
+        <v>1220</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.57393502856139</v>
+        <v>41.7410364720989</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.88930674560563</v>
+        <v>12.18832691700592</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4179546145986652</v>
+        <v>0.7118113355287545</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-2.328038008166279</v>
+        <v>-2.169192098954035</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6725</v>
+        <v>6829</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>287.8770575774263</v>
+        <v>359.3375464765434</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.87596296722534</v>
+        <v>46.48726495860494</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.25113138579644</v>
+        <v>21.81347401065535</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7877057577426284</v>
+        <v>0.4337546476543346</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.641266865236875</v>
+        <v>-2.221736879493841</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6757</v>
+        <v>6674</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>284.8741075870409</v>
+        <v>355.9338498510911</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>54.4</v>
+        <v>18.4</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.58987436695606</v>
+        <v>54.56831182373953</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>30.09215938708032</v>
+        <v>17.83284397944276</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2.487410758704088</v>
+        <v>0.5933849851091061</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0359541951719337</v>
+        <v>0.1285451377460986</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6550</v>
+        <v>6584</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>277.6497538168759</v>
+        <v>344.807163982987</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>13.4</v>
+        <v>650</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>29.54581588996828</v>
+        <v>45.77993456425428</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>34.93577668966398</v>
+        <v>12.90030106961191</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7649753816875866</v>
+        <v>0.4807163982987074</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1110774782906656</v>
+        <v>-5.721591009093643</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6530</v>
+        <v>6806</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>275.093785983843</v>
+        <v>340.507993028472</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>109.5</v>
+        <v>5.64</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>49.81907603774995</v>
+        <v>34.31641400766956</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.55406842198982</v>
+        <v>30.52195392471803</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5093785983842964</v>
+        <v>0.5507993028471946</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.270063822300699</v>
+        <v>0.2897227134509137</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6796</v>
+        <v>6722</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>274.1251216444405</v>
+        <v>333.1611204997876</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>61</v>
+        <v>39.65</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.70397082244995</v>
+        <v>54.04182376337472</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>29.76924972829878</v>
+        <v>21.41897564641932</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9125121644440513</v>
+        <v>0.8161120499787539</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.3279777503154486</v>
+        <v>0.320728459815594</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6807</v>
+        <v>6680</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>272.8705653180607</v>
+        <v>306.8850106471623</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>33.8</v>
+        <v>54.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.36797635979766</v>
+        <v>51.10347715117029</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>31.65170543277169</v>
+        <v>6.152176549584579</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.287056531806067</v>
+        <v>0.18850106471623</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.3194534875915644</v>
+        <v>0.9960605666066832</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6720</v>
+        <v>6534</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>257.8012407180428</v>
+        <v>306.0075853673343</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>148.5</v>
+        <v>90.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.75955407611241</v>
+        <v>38.29151261487883</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>25.2564966671904</v>
+        <v>13.37633721468473</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7801240718042758</v>
+        <v>0.6007585367334354</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.220194997122487</v>
+        <v>-0.6956839763803055</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6655</v>
+        <v>6510</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>243.6853494914521</v>
+        <v>300.1379619488399</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>126</v>
+        <v>3300</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.42687883837989</v>
+        <v>45.60985177798205</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7.230118812261925</v>
+        <v>17.36048420440418</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.368534949145207</v>
+        <v>1.013796194883986</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.8667255445405225</v>
+        <v>-7.543750574197901</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6674</v>
+        <v>6640</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>240.9338498510911</v>
+        <v>298.0928945901964</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>18.4</v>
+        <v>1190</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>54.56831166423766</v>
+        <v>36.63103293200506</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.83284398628646</v>
+        <v>18.57529244436268</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5933849851091061</v>
+        <v>0.8092894590196322</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1285451377842557</v>
+        <v>-21.91420700493109</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6781</v>
+        <v>6588</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>235.7215765683642</v>
+        <v>294.1795461459866</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>1135</v>
+        <v>109</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>47.45558271308458</v>
+        <v>37.5739350443592</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.9405744201623</v>
+        <v>18.88930674560563</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5721576568364154</v>
+        <v>0.4179546145986652</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-9.5876347410051</v>
+        <v>-2.328038008252133</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6830</v>
+        <v>6725</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>221.1024581879705</v>
+        <v>287.8770575774263</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>624</v>
+        <v>300</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.33453503527561</v>
+        <v>41.87596297897194</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.49471854298026</v>
+        <v>17.25113134752194</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.110245818797055</v>
+        <v>0.7877057577426284</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-13.14928156440633</v>
+        <v>-1.641266865236875</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6683</v>
+        <v>6692</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>219.8889136166768</v>
+        <v>285.6822037209404</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>1610</v>
+        <v>25.75</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.88351127799824</v>
+        <v>32.76034093803401</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.64165020514289</v>
+        <v>26.20926154950927</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.9888913616676828</v>
+        <v>0.5682203720940354</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-27.16363002915412</v>
+        <v>-0.1365155478071358</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6692</v>
+        <v>6614</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>195.6822037209404</v>
+        <v>284.0295176688121</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>25.75</v>
+        <v>39.85</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>32.76034076526444</v>
+        <v>47.66503632076125</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>26.20926150329928</v>
+        <v>12.68832064408282</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5682203720940354</v>
+        <v>0.90295176688121</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.1365155476926611</v>
+        <v>0.1644580805760876</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6722</v>
+        <v>6550</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>193.1611204997876</v>
+        <v>277.6497538168759</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>39.65</v>
+        <v>13.4</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>54.04182379445685</v>
+        <v>29.54581637595936</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>21.41897567781056</v>
+        <v>34.93577675072343</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8161120499787539</v>
+        <v>0.7649753816875866</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.3207284597869764</v>
+        <v>-0.1110774783097483</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6624</v>
+        <v>6657</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>183.5868933889686</v>
+        <v>263.3125708659723</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>47.3</v>
+        <v>38.7</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.52196874027232</v>
+        <v>42.619139609591</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.77139437646902</v>
+        <v>8.434309416871624</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.8586893388968667</v>
+        <v>1.33125708659723</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.7779157011915747</v>
+        <v>0.1689443506519491</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6657</v>
+        <v>6655</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>173.3125708659723</v>
+        <v>243.6853494914521</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>38.7</v>
+        <v>126</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>42.61913933525771</v>
+        <v>35.42687899179019</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8.434309366131858</v>
+        <v>7.230118854070986</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.33125708659723</v>
+        <v>1.368534949145207</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1689443504229963</v>
+        <v>-0.866725544922119</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6614</v>
+        <v>6781</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>169.0295176688121</v>
+        <v>235.7215765683642</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>39.85</v>
+        <v>1135</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>47.66503615413018</v>
+        <v>47.45558276770466</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.6883205838033</v>
+        <v>16.94057440908448</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.90295176688121</v>
+        <v>0.5721576568364154</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1644580805188482</v>
+        <v>-9.587634738143329</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6838</v>
+        <v>6830</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>165.6330175531716</v>
+        <v>221.1024581879705</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>25.2</v>
+        <v>624</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>37.67540960973603</v>
+        <v>40.33453504113188</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.99327814512456</v>
+        <v>13.49471840470787</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.563301755317157</v>
+        <v>1.110245818797055</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0788478317228305</v>
+        <v>-13.14928156392936</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6510</v>
+        <v>6683</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>160.1379619488399</v>
+        <v>219.8889136166768</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>3300</v>
+        <v>1610</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45.60985176665855</v>
+        <v>41.88351128620288</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.36048425232379</v>
+        <v>18.64165005323517</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.013796194883986</v>
+        <v>0.9888913616676828</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-7.543750579158782</v>
+        <v>-27.16363002810471</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6753</v>
+        <v>6504</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>156.2766062821802</v>
+        <v>210.4363711924026</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>123</v>
+        <v>36.95</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>40.62824414045193</v>
+        <v>36.3130066617473</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>9.145254785142384</v>
+        <v>12.55461313021114</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.6276606282180247</v>
+        <v>0.5436371192402601</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0327474927385131</v>
+        <v>-0.0437738677022319</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6823</v>
+        <v>6753</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>155.2875713618029</v>
+        <v>156.2766062821802</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>70.2</v>
+        <v>123</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>36.03579490537537</v>
+        <v>40.62824419742358</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>17.45135148808261</v>
+        <v>9.145254805822724</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5287571361802927</v>
+        <v>0.6276606282180247</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-1.363047212069935</v>
+        <v>-0.0327474928339479</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6504</v>
+        <v>6823</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>95.4363711924026</v>
+        <v>155.2875713618029</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>36.95</v>
+        <v>70.2</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>36.31300686063678</v>
+        <v>36.03579495709237</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>12.55461301079474</v>
+        <v>17.45135148832949</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5436371192402601</v>
+        <v>0.5287571361802927</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,11 +7195,11 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0437738681696806</v>
+        <v>-1.36304721198407</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>29.90903307117937</v>
+        <v>29.9090331595021</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>11.66658750553908</v>
+        <v>11.66658755443012</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3758288115940214</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0001493577321453</v>
+        <v>-0.0001493576939856</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
